--- a/src/data/raw/adjara_2008_results.xlsx
+++ b/src/data/raw/adjara_2008_results.xlsx
@@ -5,24 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Personal)\My projects\Elections\Results\2008_adjara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Personal)\My projects\Elections\ge_elections_dashboard\wireframe\observable_framework\elections_data\src\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5BC6A4-841D-42D8-A403-4BDF15AA66DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828B01FA-4A77-4F43-AE28-04C14ECB8431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="proportional" sheetId="1" r:id="rId1"/>
     <sheet name="majoritarian" sheetId="2" r:id="rId2"/>
     <sheet name="candidates" sheetId="3" r:id="rId3"/>
+    <sheet name="elected" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="98">
   <si>
     <t>olq</t>
   </si>
@@ -166,6 +167,156 @@
   </si>
   <si>
     <t>ხალვაში რამაზ</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>ზოსიძე</t>
+  </si>
+  <si>
+    <t>ნიაზ</t>
+  </si>
+  <si>
+    <t>ფუტკარაძე</t>
+  </si>
+  <si>
+    <t>ნუგზარ</t>
+  </si>
+  <si>
+    <t>გიორგი თარგამაძე-ქრისტიან დემოკრატები</t>
+  </si>
+  <si>
+    <t>მახარაძე</t>
+  </si>
+  <si>
+    <t>მიხეილი</t>
+  </si>
+  <si>
+    <t>ზამბახიძე</t>
+  </si>
+  <si>
+    <t>პეტრე</t>
+  </si>
+  <si>
+    <t>სურმანიძე</t>
+  </si>
+  <si>
+    <t>რამაზი</t>
+  </si>
+  <si>
+    <t>დიასამიძე</t>
+  </si>
+  <si>
+    <t>ასმათი</t>
+  </si>
+  <si>
+    <t>ცხომელიძე</t>
+  </si>
+  <si>
+    <t>გელა</t>
+  </si>
+  <si>
+    <t>ბერიძე</t>
+  </si>
+  <si>
+    <t>მურმანი</t>
+  </si>
+  <si>
+    <t>ბოლქვაძე</t>
+  </si>
+  <si>
+    <t>ვაჟა</t>
+  </si>
+  <si>
+    <t>თემური</t>
+  </si>
+  <si>
+    <t>ფარტენაძე</t>
+  </si>
+  <si>
+    <t>ბადრი</t>
+  </si>
+  <si>
+    <t>დეკანაძე</t>
+  </si>
+  <si>
+    <t>ერთიანი ნაციონალური მოძრაობა</t>
+  </si>
+  <si>
+    <t>district_code</t>
+  </si>
+  <si>
+    <t>district_name</t>
+  </si>
+  <si>
+    <t>smd</t>
+  </si>
+  <si>
+    <t>ბათუმი</t>
+  </si>
+  <si>
+    <t>ქედა</t>
+  </si>
+  <si>
+    <t>ქობულეთი</t>
+  </si>
+  <si>
+    <t>შუახევი</t>
+  </si>
+  <si>
+    <t>ხულო</t>
+  </si>
+  <si>
+    <t>გოგოტიშვილი</t>
+  </si>
+  <si>
+    <t>ზაზა</t>
+  </si>
+  <si>
+    <t>არძენაძე</t>
+  </si>
+  <si>
+    <t>რევაზი</t>
+  </si>
+  <si>
+    <t>ჭყონია</t>
+  </si>
+  <si>
+    <t>ომარი</t>
+  </si>
+  <si>
+    <t>მჟავანაძე</t>
+  </si>
+  <si>
+    <t>ხოზრევანიძე</t>
+  </si>
+  <si>
+    <t>ზურაბი</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>შაშიკაძე</t>
+  </si>
+  <si>
+    <t>ხელვაჩაური</t>
+  </si>
+  <si>
+    <t>განმეორებითი</t>
   </si>
 </sst>
 </file>
@@ -57614,4 +57765,328 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A357BCF9-E808-4575-B170-6081ADBB53C8}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>